--- a/docs/cadrage/equipe-17-sprint-backlog-v1.0.xlsx
+++ b/docs/cadrage/equipe-17-sprint-backlog-v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jstm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F10363-C481-6F4A-9EC5-9B29F54A66A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4818102A-3708-8242-B991-B68CF3B525E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garde" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,18 @@
     <sheet name="Burndown Sprint 1" sheetId="4" r:id="rId4"/>
     <sheet name="Auto-évaluation" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.5" hidden="1">'Burndown Sprint 1'!$A$8:$A$12</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'Burndown Sprint 1'!$B$7</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'Burndown Sprint 1'!$B$8:$B$12</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'Burndown Sprint 1'!$C$7</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'Burndown Sprint 1'!$C$8:$C$12</definedName>
+    <definedName name="_xlchart.v2.0" hidden="1">'Burndown Sprint 1'!$A$8:$A$12</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">'Burndown Sprint 1'!$B$7</definedName>
+    <definedName name="_xlchart.v2.2" hidden="1">'Burndown Sprint 1'!$B$8:$B$12</definedName>
+    <definedName name="_xlchart.v2.3" hidden="1">'Burndown Sprint 1'!$C$7</definedName>
+    <definedName name="_xlchart.v2.4" hidden="1">'Burndown Sprint 1'!$C$8:$C$12</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="138">
   <si>
     <t>A</t>
   </si>
@@ -73,24 +85,15 @@
     <t>Sprint concerné</t>
   </si>
   <si>
-    <t>[ Cadrage / Sprint 1 / ... / Sprint 7 ]</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>[ v1.0 · v1.1 · v2.0 ]</t>
-  </si>
-  <si>
     <t>Date de remise</t>
   </si>
   <si>
     <t>Statut</t>
   </si>
   <si>
-    <t>[ Draft · En revue PO · Validé PO · Archivé ]</t>
-  </si>
-  <si>
     <t>💡 Convention de nommage du fichier :</t>
   </si>
   <si>
@@ -142,9 +145,6 @@
     <t>Scrum Master</t>
   </si>
   <si>
-    <t>[ Prénom NOM ]</t>
-  </si>
-  <si>
     <t>Product Owner</t>
   </si>
   <si>
@@ -256,6 +256,9 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>16 h estimées · capacité 28 h-pers · marge 12 h pour onboarding, pair-programming, setup</t>
+  </si>
+  <si>
     <t>📌 STATUTS</t>
   </si>
   <si>
@@ -316,9 +319,6 @@
     <t>14h00, Début sprint</t>
   </si>
   <si>
-    <t>[à compléter]</t>
-  </si>
-  <si>
     <t>Début sprint, toutes tâches en Todo</t>
   </si>
   <si>
@@ -397,9 +397,6 @@
     <t>Métadonnées sprint complètes (numéro, date, équipe, capacité, vélocité cible, objectif, SM/PO)</t>
   </si>
   <si>
-    <t>☐ Oui   ☐ Partiel   ☐ Non</t>
-  </si>
-  <si>
     <t>Stories engagées tirées du Product Backlog avec leur ID (US-XX)</t>
   </si>
   <si>
@@ -427,120 +424,9 @@
     <t>Le Sprint Backlog a été co-construit en Sprint Planning (toutes les voix entendues)</t>
   </si>
   <si>
-    <t>Configuration du client Ollama Python + Service de Prompt Engineering (RAG local Llama 3.1 8B)</t>
-  </si>
-  <si>
-    <t>Tests pytest (mock Ollama) + Vitest interface de génération + Ajout logs de performance (&lt; 60s)</t>
-  </si>
-  <si>
-    <t>Algorithme backend de vérification automatique des réponses et calcul de la note brute sur 10</t>
-  </si>
-  <si>
-    <t>Liaison front-end du bouton "Soumettre" (payload JSON des 10 choix de l'étudiant) + redirection auto</t>
-  </si>
-  <si>
-    <t>Tests d'intégration API de soumission et vérification des cas limites (quiz incomplet, réponses vides)</t>
-  </si>
-  <si>
-    <t>Composant de feedback visuel affichant pour chaque question : choix utilisateur vs bonne réponse</t>
-  </si>
-  <si>
-    <t>Ajout du bouton "Refaire le quiz" redirigeant vers l'instance de quiz correspondante avec reset des états</t>
-  </si>
-  <si>
-    <t>Tests de régression sur le cycle complet d'historisation et validation de non-Régression UX</t>
-  </si>
-  <si>
-    <t>US-03</t>
-  </si>
-  <si>
-    <t>T-03.1</t>
-  </si>
-  <si>
-    <t>Modèles Django Quiz et Question (Foreign Key vers Course, texte, options, bonne réponse) + migration</t>
-  </si>
-  <si>
-    <t>T-03.2</t>
-  </si>
-  <si>
-    <t>T-03.3</t>
-  </si>
-  <si>
-    <t>Endpoint POST /api/quiz/generate (parsing du JSON strict retourné par Ollama et persistance)</t>
-  </si>
-  <si>
-    <t>US-04</t>
-  </si>
-  <si>
-    <t>Page React /quiz (Layout de rendu des 10 questions, état local des sélections, blocage du re-render)</t>
-  </si>
-  <si>
-    <t>T-03.4</t>
-  </si>
-  <si>
-    <t>T-03.5</t>
-  </si>
-  <si>
-    <t>T-04.1</t>
-  </si>
-  <si>
-    <t>T-04.2</t>
-  </si>
-  <si>
-    <t>T-04.3</t>
-  </si>
-  <si>
-    <t>T-04.4</t>
-  </si>
-  <si>
-    <t>Modèle Django UserResponse pour stocker les choix de l'étudiant + endpoint POST /api/quiz/&lt;id&gt;/submit</t>
-  </si>
-  <si>
-    <t>US-05</t>
-  </si>
-  <si>
-    <t>T-05.1</t>
-  </si>
-  <si>
-    <t>T-05.2</t>
-  </si>
-  <si>
-    <t>T-05.3</t>
-  </si>
-  <si>
-    <t>Endpoint GET /api/quiz/&lt;id&gt;/results renvoyant le score, le statut bon/mauvais et la correction détaillée</t>
-  </si>
-  <si>
-    <t>Page React /resultat (Affichage dynamique du score/10 avec code couleur vert/rouge)</t>
-  </si>
-  <si>
-    <t>US-06</t>
-  </si>
-  <si>
-    <t>Endpoint GET /api/history avec filtrage par user_id, tri date_created descendant et sérialiseur optimisé</t>
-  </si>
-  <si>
-    <t>T-06.1</t>
-  </si>
-  <si>
-    <t>T-06.2</t>
-  </si>
-  <si>
-    <t>T-06.3</t>
-  </si>
-  <si>
-    <t>T-06.4</t>
-  </si>
-  <si>
-    <t>Page React /historique avec affichage sous forme de tableau scannable (Titre cours, Date, Note/10)</t>
-  </si>
-  <si>
     <t>Lundi [29/06/2026, 14h00 à 18h00 (4 h)</t>
   </si>
   <si>
-    <t>[ 29/06/2026 HHhMM ]</t>
-  </si>
-  <si>
     <t>Kephren</t>
   </si>
   <si>
@@ -565,17 +451,23 @@
     <t>Stive</t>
   </si>
   <si>
-    <t>47 h estimées · capacité 28 h-pers · marge 12 h pour onboarding, pair-programming, setup</t>
-  </si>
-  <si>
     <t>☒ Oui   ☐ Partiel   ☐ Non</t>
+  </si>
+  <si>
+    <t>v1.0</t>
+  </si>
+  <si>
+    <t>29/06/2026 13h</t>
+  </si>
+  <si>
+    <t>Draft</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -715,13 +607,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF1E1B4B"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -822,7 +707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -834,7 +719,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -880,32 +764,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -921,6 +793,1062 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-FR"/>
+              <a:t>Burndown - Sprint 1</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.2680446194225725E-2"/>
+          <c:y val="0.30071886847477397"/>
+          <c:w val="0.90287510936132986"/>
+          <c:h val="0.56423447069116361"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Burndown Sprint 1'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Heure restante (idéal)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Burndown Sprint 1'!$A$8:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>14h00, Début sprint</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15h00, Daily intermédiaire</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16h00, Mi-sprint</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17h00, Avant clôture</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18h00, Fin sprint / Review</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Burndown Sprint 1'!$B$8:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9F42-BD44-8284-EE8D258EBB35}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Burndown Sprint 1'!$C$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Heure restante (réel)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Burndown Sprint 1'!$A$8:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>14h00, Début sprint</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15h00, Daily intermédiaire</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16h00, Mi-sprint</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17h00, Avant clôture</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18h00, Fin sprint / Review</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Burndown Sprint 1'!$C$8:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9F42-BD44-8284-EE8D258EBB35}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="780391744"/>
+        <c:axId val="780805264"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="780391744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="780805264"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="780805264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="780391744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>565150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Graphique 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB99FDFF-03FB-8B40-B35D-F77B245247C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1279,7 +2207,7 @@
       <c r="B5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="37">
         <v>17</v>
       </c>
     </row>
@@ -1287,50 +2215,50 @@
       <c r="B6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="39" t="s">
-        <v>170</v>
+      <c r="C6" s="34" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>12</v>
+      <c r="C7" s="34" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>167</v>
+        <v>13</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B12" s="12" t="s">
-        <v>18</v>
+      <c r="B12" s="11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1340,7 +2268,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -1351,772 +2279,404 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>20</v>
+      <c r="A1" s="12" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="B6" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B7" s="33" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+    <row r="8" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="38" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+      <c r="B8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="38" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+      <c r="B9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="15" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
+      <c r="B10" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="15" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+      <c r="B11" s="33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>35</v>
+      <c r="B12" s="33" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B17" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="s">
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B19" s="17" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="s">
+      <c r="C19" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="D19" s="17" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="18" t="s">
+      <c r="E19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="F19" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="G19" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="B20" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="D20" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="20">
+        <v>1</v>
+      </c>
+      <c r="F20" s="20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="18" t="s">
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="20">
+        <v>2</v>
+      </c>
+      <c r="F21" s="20">
+        <v>2</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="20">
+        <v>3</v>
+      </c>
+      <c r="F22" s="20">
+        <v>3</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" s="20">
+        <v>1</v>
+      </c>
+      <c r="F23" s="20">
+        <v>1</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="23">
+        <v>1</v>
+      </c>
+      <c r="F24" s="23">
+        <v>1</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" s="23">
+        <v>3</v>
+      </c>
+      <c r="F25" s="23">
+        <v>3</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="23">
+        <v>1</v>
+      </c>
+      <c r="F26" s="23">
+        <v>1</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" s="23">
+        <v>3</v>
+      </c>
+      <c r="F27" s="23">
+        <v>3</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="23">
+        <v>1</v>
+      </c>
+      <c r="F28" s="23">
+        <v>1</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24">
+        <f>SUM(E20:E28)</f>
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="E20" s="21">
-        <v>1</v>
-      </c>
-      <c r="F20" s="21">
-        <v>1</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="21">
-        <v>2</v>
-      </c>
-      <c r="F21" s="21">
-        <v>2</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="E22" s="21">
-        <v>3</v>
-      </c>
-      <c r="F22" s="21">
-        <v>3</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" s="21">
-        <v>1</v>
-      </c>
-      <c r="F23" s="21">
-        <v>1</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="E24" s="24">
-        <v>1</v>
-      </c>
-      <c r="F24" s="24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="E25" s="24">
-        <v>3</v>
-      </c>
-      <c r="F25" s="24">
-        <v>3</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" s="24">
-        <v>1</v>
-      </c>
-      <c r="F26" s="24">
-        <v>1</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="E27" s="24">
-        <v>3</v>
-      </c>
-      <c r="F27" s="24">
-        <v>3</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="22" t="s">
+      <c r="F29" s="24">
+        <f>SUM(F20:F28)</f>
+        <v>16</v>
+      </c>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="23" t="s">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" s="24">
-        <v>1</v>
-      </c>
-      <c r="F28" s="24">
-        <v>1</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="E29" s="21">
-        <v>2</v>
-      </c>
-      <c r="F29" s="21">
-        <v>2</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E30" s="21">
-        <v>3</v>
-      </c>
-      <c r="F30" s="21">
-        <v>3</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="E31" s="21">
-        <v>3</v>
-      </c>
-      <c r="F31" s="21">
-        <v>3</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="E32" s="21">
-        <v>3</v>
-      </c>
-      <c r="F32" s="21">
-        <v>3</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="E33" s="21">
-        <v>2</v>
-      </c>
-      <c r="F33" s="21">
-        <v>2</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="E34" s="24">
-        <v>2</v>
-      </c>
-      <c r="F34" s="24">
-        <v>2</v>
-      </c>
-      <c r="G34" s="35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="B35" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="E35" s="24">
-        <v>1</v>
-      </c>
-      <c r="F35" s="24">
-        <v>1</v>
-      </c>
-      <c r="G35" s="35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="B36" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36" s="24">
-        <v>2</v>
-      </c>
-      <c r="F36" s="24">
-        <v>2</v>
-      </c>
-      <c r="G36" s="35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="B37" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C37" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="E37" s="24">
-        <v>1</v>
-      </c>
-      <c r="F37" s="24">
-        <v>1</v>
-      </c>
-      <c r="G37" s="35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="E38" s="37">
-        <v>2</v>
-      </c>
-      <c r="F38" s="37">
-        <v>2</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="B39" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="E39" s="37">
-        <v>2</v>
-      </c>
-      <c r="F39" s="37">
-        <v>2</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40" s="37">
-        <v>2</v>
-      </c>
-      <c r="F40" s="37">
-        <v>2</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="B41" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="E41" s="40">
-        <v>2</v>
-      </c>
-      <c r="F41" s="40">
-        <v>2</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="B42" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="E42" s="40">
-        <v>2</v>
-      </c>
-      <c r="F42" s="40">
-        <v>2</v>
-      </c>
-      <c r="G42" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="B43" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="E43" s="40">
-        <v>1</v>
-      </c>
-      <c r="F43" s="40">
-        <v>1</v>
-      </c>
-      <c r="G43" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="B44" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="E44" s="40">
-        <v>1</v>
-      </c>
-      <c r="F44" s="40">
-        <v>1</v>
-      </c>
-      <c r="G44" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="25" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="26"/>
-      <c r="C45" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="D45" s="26"/>
-      <c r="E45" s="25">
-        <f>SUM(E20:E44)</f>
-        <v>47</v>
-      </c>
-      <c r="F45" s="25">
-        <f>SUM(F20:F44)</f>
-        <v>47</v>
-      </c>
-      <c r="G45" s="26"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+      <c r="B33" s="9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="9" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="28" t="s">
+      <c r="B34" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="9" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="15" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="17" t="s">
+      <c r="B35" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>80</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2133,170 +2693,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>81</v>
+      <c r="A1" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C7" s="17" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="18" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="B8" s="29">
+        <v>16</v>
+      </c>
+      <c r="C8" s="29">
+        <v>16</v>
+      </c>
+      <c r="D8" s="29">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="18" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="28" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="29" t="s">
+      <c r="B9" s="29">
+        <v>12</v>
+      </c>
+      <c r="C9" s="29">
+        <v>13</v>
+      </c>
+      <c r="D9" s="29">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="30">
-        <v>16</v>
-      </c>
-      <c r="C8" s="30" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="15" t="s">
+      <c r="B10" s="29">
+        <v>8</v>
+      </c>
+      <c r="C10" s="29">
+        <v>10</v>
+      </c>
+      <c r="D10" s="29">
+        <v>2</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29" t="s">
+    <row r="11" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="30">
-        <v>12</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="15" t="s">
+      <c r="B11" s="29">
+        <v>4</v>
+      </c>
+      <c r="C11" s="29">
+        <v>3</v>
+      </c>
+      <c r="D11" s="29">
+        <v>-1</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="29" t="s">
+    <row r="12" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="30">
-        <v>8</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="15" t="s">
+      <c r="B12" s="29">
+        <v>0</v>
+      </c>
+      <c r="C12" s="29">
+        <v>0</v>
+      </c>
+      <c r="D12" s="29">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="30">
-        <v>4</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="30">
-        <v>0</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="15" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B20" s="9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="28" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B21" s="9" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2313,115 +2884,115 @@
   <sheetData>
     <row r="2" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B3" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="30" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18" t="s">
+      <c r="C6" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="30"/>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C7" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="30"/>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C8" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="30"/>
+    </row>
+    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="30" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="31" t="s">
+      <c r="C9" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="30"/>
+    </row>
+    <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="D6" s="31"/>
-    </row>
-    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="31" t="s">
+      <c r="C10" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="30"/>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" s="30"/>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="D7" s="31"/>
-    </row>
-    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="31" t="s">
+      <c r="C12" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" s="30"/>
+    </row>
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="D8" s="31"/>
-    </row>
-    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="31" t="s">
+      <c r="C13" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="30"/>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="31"/>
-    </row>
-    <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="31" t="s">
+      <c r="C14" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="30"/>
+    </row>
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="D10" s="31"/>
-    </row>
-    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="D11" s="31"/>
-    </row>
-    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="31"/>
-    </row>
-    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="31"/>
-    </row>
-    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="31"/>
-    </row>
-    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" s="31"/>
+      <c r="C15" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
